--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,2009 +429,2667 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>team_home</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_away</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>team_away</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45529.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>pWQQJq6l</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Leuna Chemie Stadion
  (Halle)</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="E11" t="n">
         <v>15057</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hallescher</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
         <v>593</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>BRITA-Arena
  (Wiesbaden)</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="E12" t="n">
         <v>12566</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Wehen</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>59</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
         <v>593</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Flyeralarm Arena
  (Wurzburger)</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="E13" t="n">
         <v>13090</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Wurzburger Kickers</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
         <v>593</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45520.65625</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Donaustadion
  (Ulm)</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="E14" t="n">
         <v>19500</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ulm</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>59</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
         <v>593</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Erzgebirgsstadion
  (Aue)</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="E15" t="n">
         <v>16485</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aue</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>59</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
         <v>593</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B16" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bruchwegstadion
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schott Mainz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>593</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>45521.33333333334</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>WzEYqEyg</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Schott Mainz</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Greuther Furth</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>59</v>
-      </c>
-      <c r="N7" t="n">
-        <v>593</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>OSTALB ARENA
  (Aalen)</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="E17" t="n">
         <v>14500</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Aalen</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>59</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
         <v>593</v>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Volksstadion Greifswald
  (Greifswald)</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="E18" t="n">
         <v>4990</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Greifswald</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>59</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
         <v>593</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Audi Sportpark
  (Ingolstadt)</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="E19" t="n">
         <v>15800</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Ingolstadt</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>59</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
         <v>593</v>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadion an der Hafenstrasse
  (Essen)</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="E20" t="n">
         <v>20352</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>RW Essen</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>59</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="K20" t="n">
+        <v>59</v>
+      </c>
+      <c r="L20" t="n">
         <v>593</v>
       </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadion an der Bremer Brück
  (Osnabrück)</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="E21" t="n">
         <v>16667</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>VfL Osnabruck</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="K21" t="n">
+        <v>59</v>
+      </c>
+      <c r="L21" t="n">
         <v>593</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>MS Technologie Arena
  (Villingen-Schwenningen)</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="E22" t="n">
         <v>8000</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Villingen</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>59</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" t="n">
         <v>593</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>New Tivoli
  (Aachen)</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="E23" t="n">
         <v>31026</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Alemannia Aachen</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>59</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="K23" t="n">
+        <v>59</v>
+      </c>
+      <c r="L23" t="n">
         <v>593</v>
       </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Schüco Arena
  (Bielefeld)</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="E24" t="n">
         <v>27332</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Arminia Bielefeld</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Hannover</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>59</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="K24" t="n">
+        <v>59</v>
+      </c>
+      <c r="L24" t="n">
         <v>593</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Stadion Lohmühle
  (Lubeck)</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="E25" t="n">
         <v>17849</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Phonix Lubeck</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>59</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
         <v>593</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Ludwigspark Stadion
  (Saarbrücken)</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="E26" t="n">
         <v>16003</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Saarbrucken</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>59</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="K26" t="n">
+        <v>59</v>
+      </c>
+      <c r="L26" t="n">
         <v>593</v>
       </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B27" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Friedrich Ludwig Jahn Sportpark
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>19708</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Viktoria Berlin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="L27" t="n">
+        <v>593</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>59</v>
-      </c>
-      <c r="N18" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stadion am Panzenberg
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bremer</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>59</v>
+      </c>
+      <c r="L28" t="n">
         <v>593</v>
       </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>59</v>
-      </c>
-      <c r="N19" t="n">
-        <v>593</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ostseestadion
  (Rostock)</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="E29" t="n">
         <v>29000</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Hansa Rostock</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>59</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+      <c r="L29" t="n">
         <v>593</v>
       </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Friedrich-Ebert-Stadium
  (Hildesheim)</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="E30" t="n">
         <v>10000</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Hildesheim</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>59</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="K30" t="n">
+        <v>59</v>
+      </c>
+      <c r="L30" t="n">
         <v>593</v>
       </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Jahnstadion Regensburg
  (Regensburg)</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="E31" t="n">
         <v>15210</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>59</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="K31" t="n">
+        <v>59</v>
+      </c>
+      <c r="L31" t="n">
         <v>593</v>
       </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Hardtwaldstadion
  (Sandhausen)</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="E32" t="n">
         <v>15414</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sandhausen</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>59</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="K32" t="n">
+        <v>59</v>
+      </c>
+      <c r="L32" t="n">
         <v>593</v>
       </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B33" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Teutonia Ottensen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>59</v>
+      </c>
+      <c r="L33" t="n">
+        <v>593</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>59</v>
-      </c>
-      <c r="N24" t="n">
-        <v>593</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Stadion am Lotter Kreuz
  (Lotte)</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="E34" t="n">
         <v>10059</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Lotte</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>59</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="L34" t="n">
         <v>593</v>
       </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Hansch-Arena
  (Meppen)</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="E35" t="n">
         <v>13696</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Meppen</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>59</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="K35" t="n">
+        <v>59</v>
+      </c>
+      <c r="L35" t="n">
         <v>593</v>
       </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Rudolf-Harbig-Stadion
  (Dresden)</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="E36" t="n">
         <v>32249</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SG Dynamo Dresden</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>59</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="K36" t="n">
+        <v>59</v>
+      </c>
+      <c r="L36" t="n">
         <v>593</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Stadion der Freundschaft
  (Cottbus)</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="E37" t="n">
         <v>22450</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Cottbus</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>59</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="K37" t="n">
+        <v>59</v>
+      </c>
+      <c r="L37" t="n">
         <v>593</v>
       </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Bieberer Berg Stadion
  (Offenbach am Main)</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="E38" t="n">
         <v>20500</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Offenbach</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>59</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="K38" t="n">
+        <v>59</v>
+      </c>
+      <c r="L38" t="n">
         <v>593</v>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Stadion Oberwerth
  (Koblenz)</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="E39" t="n">
         <v>9500</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>TuS Koblenz</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>59</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="K39" t="n">
+        <v>59</v>
+      </c>
+      <c r="L39" t="n">
         <v>593</v>
       </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45523.65625</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Eintracht-Stadion
  (Braunschweig)</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="E40" t="n">
         <v>23325</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>59</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="K40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L40" t="n">
         <v>593</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>20242025</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>12794</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
+        <v>593</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
+      <c r="B42" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>BayArena
  (Leverkusen)</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="E42" t="n">
         <v>30210</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>59</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="K42" t="n">
+        <v>59</v>
+      </c>
+      <c r="L42" t="n">
         <v>594</v>
       </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
         <v>2024</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,1951 +575,2455 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45529.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Leuna Chemie Stadion
  (Halle)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E11" t="n">
         <v>15057</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hallescher</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
         <v>593</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>BRITA-Arena
  (Wiesbaden)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E12" t="n">
         <v>12566</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Wehen</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
         <v>593</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Flyeralarm Arena
  (Wurzburger)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E13" t="n">
         <v>13090</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Wurzburger Kickers</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
         <v>593</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45520.65625</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Donaustadion
  (Ulm)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E14" t="n">
         <v>19500</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ulm</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
         <v>593</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Erzgebirgsstadion
  (Aue)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E15" t="n">
         <v>16485</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aue</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
         <v>593</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Bruchwegstadion
  (Mainz)</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E16" t="n">
         <v>7134</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>WzEYqEyg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Schott Mainz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
         <v>593</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>OSTALB ARENA
  (Aalen)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E17" t="n">
         <v>14500</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Aalen</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Schalke</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
         <v>593</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Volksstadion Greifswald
  (Greifswald)</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E18" t="n">
         <v>4990</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Greifswald</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
         <v>593</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Audi Sportpark
  (Ingolstadt)</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E19" t="n">
         <v>15800</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Ingolstadt</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
         <v>593</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadion an der Hafenstrasse
  (Essen)</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E20" t="n">
         <v>20352</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>RW Essen</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K20" t="n">
+        <v>59</v>
+      </c>
+      <c r="L20" t="n">
         <v>593</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadion an der Bremer Brück
  (Osnabrück)</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E21" t="n">
         <v>16667</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>VfL Osnabruck</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K21" t="n">
+        <v>59</v>
+      </c>
+      <c r="L21" t="n">
         <v>593</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>MS Technologie Arena
  (Villingen-Schwenningen)</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E22" t="n">
         <v>8000</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Villingen</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" t="n">
         <v>593</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="N22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>New Tivoli
  (Aachen)</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E23" t="n">
         <v>31026</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Alemannia Aachen</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K23" t="n">
+        <v>59</v>
+      </c>
+      <c r="L23" t="n">
         <v>593</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="N23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Schüco Arena
  (Bielefeld)</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E24" t="n">
         <v>27332</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Arminia Bielefeld</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Hannover</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K24" t="n">
+        <v>59</v>
+      </c>
+      <c r="L24" t="n">
         <v>593</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Stadion Lohmühle
  (Lubeck)</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E25" t="n">
         <v>17849</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Phonix Lubeck</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
         <v>593</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="N25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Ludwigspark Stadion
  (Saarbrücken)</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E26" t="n">
         <v>16003</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Saarbrucken</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K26" t="n">
+        <v>59</v>
+      </c>
+      <c r="L26" t="n">
         <v>593</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Friedrich Ludwig Jahn Sportpark
  (Berlin)</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E27" t="n">
         <v>19708</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>UNr2EUfd</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Viktoria Berlin</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="L27" t="n">
         <v>593</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="N27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>YV3TqwPH</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Stadion am Panzenberg
  (Bremen)</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E28" t="n">
         <v>5000</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>tW75B1ei</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Bremer</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>G2Op923t</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>59</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K28" t="n">
+        <v>59</v>
+      </c>
+      <c r="L28" t="n">
         <v>593</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="N28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>l0ueP5rR</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B29" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ostseestadion
  (Rostock)</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E29" t="n">
         <v>29000</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Hansa Rostock</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>59</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+      <c r="L29" t="n">
         <v>593</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="N29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Friedrich-Ebert-Stadium
  (Hildesheim)</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E30" t="n">
         <v>10000</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Hildesheim</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>59</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K30" t="n">
+        <v>59</v>
+      </c>
+      <c r="L30" t="n">
         <v>593</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="N30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Jahnstadion Regensburg
  (Regensburg)</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E31" t="n">
         <v>15210</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bochum</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>59</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K31" t="n">
+        <v>59</v>
+      </c>
+      <c r="L31" t="n">
         <v>593</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="N31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Hardtwaldstadion
  (Sandhausen)</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E32" t="n">
         <v>15414</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sandhausen</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>59</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K32" t="n">
+        <v>59</v>
+      </c>
+      <c r="L32" t="n">
         <v>593</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
  (Hamburg)</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E33" t="n">
         <v>29546</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>WrbkcjCd</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Teutonia Ottensen</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>S0hPB9rA</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Darmstadt</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>59</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K33" t="n">
+        <v>59</v>
+      </c>
+      <c r="L33" t="n">
         <v>593</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Stadion am Lotter Kreuz
  (Lotte)</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E34" t="n">
         <v>10059</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Lotte</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="L34" t="n">
         <v>593</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Hansch-Arena
  (Meppen)</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E35" t="n">
         <v>13696</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Meppen</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K35" t="n">
+        <v>59</v>
+      </c>
+      <c r="L35" t="n">
         <v>593</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="N35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Rudolf-Harbig-Stadion
  (Dresden)</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E36" t="n">
         <v>32249</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SG Dynamo Dresden</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K36" t="n">
+        <v>59</v>
+      </c>
+      <c r="L36" t="n">
         <v>593</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="N36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Stadion der Freundschaft
  (Cottbus)</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E37" t="n">
         <v>22450</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Cottbus</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K37" t="n">
+        <v>59</v>
+      </c>
+      <c r="L37" t="n">
         <v>593</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="N37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Bieberer Berg Stadion
  (Offenbach am Main)</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E38" t="n">
         <v>20500</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Offenbach</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K38" t="n">
+        <v>59</v>
+      </c>
+      <c r="L38" t="n">
         <v>593</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="N38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Stadion Oberwerth
  (Koblenz)</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E39" t="n">
         <v>9500</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>TuS Koblenz</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K39" t="n">
+        <v>59</v>
+      </c>
+      <c r="L39" t="n">
         <v>593</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="N39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45523.65625</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Eintracht-Stadion
  (Braunschweig)</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E40" t="n">
         <v>23325</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L40" t="n">
         <v>593</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="N40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B41" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>BayArena
  (Leverkusen)</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E41" t="n">
         <v>30210</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
         <v>594</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N41" t="n">
         <v>2024</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Super Cup</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,31 +1079,31 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leuna Chemie Stadion
- (Halle)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15057</v>
+        <v>22012</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1120,10 +1120,10 @@
         <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>20242025</v>
@@ -1135,58 +1135,58 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BRITA-Arena
- (Wiesbaden)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12566</v>
+        <v>26000</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wehen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>20242025</v>
@@ -1198,38 +1198,38 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flyeralarm Arena
- (Wurzburger)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13090</v>
+        <v>58000</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1246,10 +1246,10 @@
         <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>20242025</v>
@@ -1261,58 +1261,58 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Donaustadion
- (Ulm)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19500</v>
+        <v>15034</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>59</v>
       </c>
       <c r="L14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>20242025</v>
@@ -1324,58 +1324,58 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erzgebirgsstadion
- (Aue)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16485</v>
+        <v>60449</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aue</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>20242025</v>
@@ -1387,58 +1387,58 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bruchwegstadion
- (Mainz)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7134</v>
+        <v>42100</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schott Mainz</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Greuther Furth</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>59</v>
       </c>
       <c r="L16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>20242025</v>
@@ -1450,58 +1450,58 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSTALB ARENA
- (Aalen)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14500</v>
+        <v>30210</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aalen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>20242025</v>
@@ -1513,58 +1513,58 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Volksstadion Greifswald
- (Greifswald)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4990</v>
+        <v>15000</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Greifswald</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>20242025</v>
@@ -1576,58 +1576,58 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Audi Sportpark
- (Ingolstadt)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15800</v>
+        <v>75024</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>20242025</v>
@@ -1639,48 +1639,53 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stadion an der Hafenstrasse
- (Essen)</t>
+          <t>Stadion der Freundschaft
+ (Cottbus)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20352</v>
+        <v>22450</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RW Essen</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1709,41 +1714,46 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stadion an der Bremer Brück
- (Osnabrück)</t>
+          <t>Bieberer Berg Stadion
+ (Offenbach am Main)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16667</v>
+        <v>20500</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Offenbach</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1772,41 +1782,46 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MS Technologie Arena
- (Villingen-Schwenningen)</t>
+          <t>Stadion Oberwerth
+ (Koblenz)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8000</v>
+        <v>9500</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>p8wBsqZt</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Villingen</t>
+          <t>TuS Koblenz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1835,41 +1850,46 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>45523.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>New Tivoli
- (Aachen)</t>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31026</v>
+        <v>23325</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1898,41 +1918,41 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45531.65625</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Schüco Arena
- (Bielefeld)</t>
+          <t>Preussenstadion
+ (Munster)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27332</v>
+        <v>12794</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Preussen Munster</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hannover</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1961,41 +1981,41 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45532.54166666666</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stadion Lohmühle
- (Lubeck)</t>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17849</v>
+        <v>10445</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Phonix Lubeck</t>
+          <t>Jena</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2018,1014 +2038,6 @@
       <c r="P25" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Ludwigspark Stadion
- (Saarbrücken)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>16003</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Saarbrucken</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nurnberg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
-        <v>593</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Friedrich Ludwig Jahn Sportpark
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>19708</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
-        <v>593</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Stadion am Panzenberg
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
-        <v>593</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ostseestadion
- (Rostock)</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Hansa Rostock</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Hertha Berlin</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
-        <v>593</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Friedrich-Ebert-Stadium
- (Hildesheim)</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Hildesheim</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Elversberg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
-        <v>593</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jahnstadion Regensburg
- (Regensburg)</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
-        <v>593</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Hardtwaldstadion
- (Sandhausen)</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>15414</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sandhausen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
-        <v>593</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
-        <v>593</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Stadion am Lotter Kreuz
- (Lotte)</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10059</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Lotte</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>59</v>
-      </c>
-      <c r="L34" t="n">
-        <v>593</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hansch-Arena
- (Meppen)</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>13696</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Meppen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Hamburger SV</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>59</v>
-      </c>
-      <c r="L35" t="n">
-        <v>593</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Rudolf-Harbig-Stadion
- (Dresden)</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32249</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SG Dynamo Dresden</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Dusseldorf</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>59</v>
-      </c>
-      <c r="L36" t="n">
-        <v>593</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Stadion der Freundschaft
- (Cottbus)</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Cottbus</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>59</v>
-      </c>
-      <c r="L37" t="n">
-        <v>593</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bieberer Berg Stadion
- (Offenbach am Main)</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Offenbach</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magdeburg</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>59</v>
-      </c>
-      <c r="L38" t="n">
-        <v>593</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Stadion Oberwerth
- (Koblenz)</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TuS Koblenz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>59</v>
-      </c>
-      <c r="L39" t="n">
-        <v>593</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Eintracht-Stadion
- (Braunschweig)</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>59</v>
-      </c>
-      <c r="L40" t="n">
-        <v>593</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>59</v>
-      </c>
-      <c r="L41" t="n">
-        <v>594</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,31 +1079,31 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leuna Chemie Stadion
- (Halle)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15057</v>
+        <v>22012</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1120,10 +1120,10 @@
         <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>20242025</v>
@@ -1135,58 +1135,58 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BRITA-Arena
- (Wiesbaden)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12566</v>
+        <v>26000</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wehen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>20242025</v>
@@ -1198,38 +1198,38 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flyeralarm Arena
- (Wurzburger)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13090</v>
+        <v>58000</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1246,10 +1246,10 @@
         <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>20242025</v>
@@ -1261,58 +1261,58 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Donaustadion
- (Ulm)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19500</v>
+        <v>15034</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>59</v>
       </c>
       <c r="L14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>20242025</v>
@@ -1324,58 +1324,58 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erzgebirgsstadion
- (Aue)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16485</v>
+        <v>60449</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aue</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>20242025</v>
@@ -1387,58 +1387,58 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bruchwegstadion
- (Mainz)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7134</v>
+        <v>42100</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schott Mainz</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Greuther Furth</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>59</v>
       </c>
       <c r="L16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>20242025</v>
@@ -1450,58 +1450,58 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSTALB ARENA
- (Aalen)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14500</v>
+        <v>30210</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aalen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>20242025</v>
@@ -1513,58 +1513,58 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Volksstadion Greifswald
- (Greifswald)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4990</v>
+        <v>15000</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Greifswald</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>20242025</v>
@@ -1576,58 +1576,58 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Audi Sportpark
- (Ingolstadt)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15800</v>
+        <v>75024</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>20242025</v>
@@ -1639,48 +1639,48 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45531.65625</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stadion an der Hafenstrasse
- (Essen)</t>
+          <t>Preussenstadion
+ (Munster)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20352</v>
+        <v>12794</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RW Essen</t>
+          <t>Preussen Munster</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1709,41 +1709,41 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45532.54166666666</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stadion an der Bremer Brück
- (Osnabrück)</t>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16667</v>
+        <v>10445</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Jena</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1766,1266 +1766,6 @@
       <c r="P21" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MS Technologie Arena
- (Villingen-Schwenningen)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>lKLJUxeT</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Villingen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>59</v>
-      </c>
-      <c r="L22" t="n">
-        <v>593</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>New Tivoli
- (Aachen)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>31026</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>j3PKcB4E</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Alemannia Aachen</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>59</v>
-      </c>
-      <c r="L23" t="n">
-        <v>593</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Schüco Arena
- (Bielefeld)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>27332</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>pp38UXK8</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Arminia Bielefeld</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Hannover</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>59</v>
-      </c>
-      <c r="L24" t="n">
-        <v>593</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stadion Lohmühle
- (Lubeck)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>17849</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>I1Vk6k3R</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Phonix Lubeck</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>59</v>
-      </c>
-      <c r="L25" t="n">
-        <v>593</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Ludwigspark Stadion
- (Saarbrücken)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>16003</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Saarbrucken</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nurnberg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
-        <v>593</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Friedrich Ludwig Jahn Sportpark
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>19708</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
-        <v>593</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Stadion am Panzenberg
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
-        <v>593</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ostseestadion
- (Rostock)</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Hansa Rostock</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Hertha Berlin</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
-        <v>593</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Friedrich-Ebert-Stadium
- (Hildesheim)</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Hildesheim</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Elversberg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
-        <v>593</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jahnstadion Regensburg
- (Regensburg)</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
-        <v>593</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Hardtwaldstadion
- (Sandhausen)</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>15414</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sandhausen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
-        <v>593</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
-        <v>593</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Stadion am Lotter Kreuz
- (Lotte)</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10059</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Lotte</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>59</v>
-      </c>
-      <c r="L34" t="n">
-        <v>593</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hansch-Arena
- (Meppen)</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>13696</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Meppen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Hamburger SV</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>59</v>
-      </c>
-      <c r="L35" t="n">
-        <v>593</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Rudolf-Harbig-Stadion
- (Dresden)</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32249</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SG Dynamo Dresden</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Dusseldorf</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>59</v>
-      </c>
-      <c r="L36" t="n">
-        <v>593</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Stadion der Freundschaft
- (Cottbus)</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Cottbus</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>59</v>
-      </c>
-      <c r="L37" t="n">
-        <v>593</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bieberer Berg Stadion
- (Offenbach am Main)</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Offenbach</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magdeburg</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>59</v>
-      </c>
-      <c r="L38" t="n">
-        <v>593</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Stadion Oberwerth
- (Koblenz)</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TuS Koblenz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>59</v>
-      </c>
-      <c r="L39" t="n">
-        <v>593</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Eintracht-Stadion
- (Braunschweig)</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>59</v>
-      </c>
-      <c r="L40" t="n">
-        <v>593</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>59</v>
-      </c>
-      <c r="L41" t="n">
-        <v>594</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,132 +1643,6 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Preussenstadion
- (Munster)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>12794</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Preussen Munster</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>59</v>
-      </c>
-      <c r="L20" t="n">
-        <v>593</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45532.54166666666</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Ernst Abbe Sportfeld
- (Jena)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>10445</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>APNl8MIn</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jena</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>59</v>
-      </c>
-      <c r="L21" t="n">
-        <v>593</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stegemann S.
+          <t>Siebert D.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>28917</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Welz T.
+          <t>Jablonski S.
  (Ger)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34700</v>
+        <v>29546</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Stieler T.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30150</v>
+        <v>22012</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +711,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Osmers H.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mewa Arena
- (Mainz)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34000</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +774,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47069</v>
+        <v>58000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +837,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>81365</v>
+        <v>15034</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -912,6 +892,321 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Siebert D.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28917</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29546</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22012</v>
+        <v>58000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -711,7 +701,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -720,32 +710,32 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>15034</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -774,7 +764,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -783,32 +773,32 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58000</v>
+        <v>60449</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -837,7 +827,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -846,32 +836,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -900,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60449</v>
+        <v>30210</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -963,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42100</v>
+        <v>15000</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1026,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30210</v>
+        <v>75024</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1081,132 +1071,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.4375</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.52083333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.64583333334</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.4375</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22012</v>
+        <v>26000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26000</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>15034</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,376 +716,769 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45548.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Holstein-Stadion
  (Kiel)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E16" t="n">
         <v>15034</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>59</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L16" t="n">
         <v>591</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N16" t="n">
         <v>20242025</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45535.4375</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MHPArena
- (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>591</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45535.4375</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.4375</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.52083333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15000</v>
+        <v>81365</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.4375</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Allianz Arena
- (Munich)</t>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>54042</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -630,6 +630,447 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,573 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,18 +512,13 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WWK Arena
@@ -546,12 +541,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,66 +575,1069 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45556.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Mewa Arena
  (Mainz)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E14" t="n">
         <v>34000</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>591</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.64583333334</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45556.4375</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>26000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15000</v>
+        <v>22012</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>42100</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.4375</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45556.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>58000</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.5625</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45557.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58000</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45557.4375</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30210</v>
+        <v>60449</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.52083333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60449</v>
+        <v>29546</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,636 +1048,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.60416666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>54042</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.4375</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>15034</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,134 +512,1132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>WWK Arena
  (Augsburg)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>30660</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L2" t="n">
-        <v>591</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>591</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45562.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Signal Iduna Park
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Borussia-Park
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Europa-Park Stadion
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Volkswagen Arena
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45563.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Allianz Arena
@@ -1071,573 +1106,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WWK Arena
- (Augsburg)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30660</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.4375</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MHPArena
- (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.64583333334</v>
+        <v>45564.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brych F.
+          <t>Stieler T.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81365</v>
+        <v>15034</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.4375</v>
+        <v>45564.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Schlager D.
+          <t>Reichel T.
  (Ger)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>PreZero Arena
+ (Sinsheim)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54042</v>
+        <v>30150</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -640,472 +640,6 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Gerach T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
-        <v>591</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Exner F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
-        <v>591</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Siebert D.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>591</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.4375</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>15034</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.4375</v>
+        <v>45569.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stieler T.
+          <t>Badstubner F.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>WWK Arena
+ (Augsburg)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15034</v>
+        <v>30660</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,66 +580,900 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
+        <v>45570.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Reichel T.
  (Ger)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>PreZero Arena
  (Sinsheim)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E15" t="n">
         <v>30150</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L15" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N15" t="n">
         <v>20242025</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.64583333334</v>
+        <v>45571.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Badstubner F.
+          <t>Stegemann S.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>15000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30210</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -643,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burda M.
+          <t>Osmers H.
  (Ger)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>60449</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -711,46 +716,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reichel T.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>81365</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -779,46 +779,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Welz T.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45584.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>54042</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -847,46 +842,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dingert C.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45584.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29546</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -915,41 +905,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15000</v>
+        <v>34700</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -978,41 +968,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>PreZero Arena
+ (Sinsheim)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58000</v>
+        <v>30150</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1041,41 +1031,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>Mewa Arena
+ (Mainz)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60449</v>
+        <v>34000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1104,41 +1094,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>81365</v>
+        <v>75024</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1167,41 +1157,41 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>54042</v>
+        <v>15034</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1230,41 +1220,41 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30210</v>
+        <v>28917</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1285,195 +1275,6 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45583.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Signal Iduna Park

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,124 +512,1132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Holstein-Stadion
  (Kiel)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E15" t="n">
         <v>15034</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L2" t="n">
-        <v>591</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Volkswagen Arena
  (Wolfsburg)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E16" t="n">
         <v>28917</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>591</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>WWK Arena
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>MHPArena
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Weserstadion
@@ -1071,573 +1101,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>15034</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.47916666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>54042</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,595 +512,1132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.64583333334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Petersen M.
- (Ger)</t>
-        </is>
-      </c>
+        <v>45597.6875</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45604.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Mewa Arena
  (Mainz)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E13" t="n">
         <v>34000</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>59</v>
-      </c>
-      <c r="L2" t="n">
-        <v>591</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45591.4375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Welz T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>WWK Arena
  (Augsburg)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E17" t="n">
         <v>30660</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>591</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45591.4375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
-        <v>591</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45591.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reichel T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
-        <v>591</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45591.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hartmann R.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>MHPArena
  (Stuttgart)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E18" t="n">
         <v>60449</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>591</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45591.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Badstubner F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45592.47916666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45592.5625</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45592.64583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Voith-Arena
  (Heidenheim)</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E19" t="n">
         <v>15000</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,573 +1071,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.47916666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>WWK Arena
- (Augsburg)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>30660</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.5625</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MHPArena
- (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.64583333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -512,41 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.6875</v>
+        <v>45604.6875</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30210</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Allianz Arena
- (Munich)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>Mewa Arena
+ (Mainz)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>34000</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30150</v>
+        <v>29546</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
+          <t>Red Bull Arena
+ (Leipzig)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28917</v>
+        <v>47069</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>WWK Arena
+ (Augsburg)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81365</v>
+        <v>30660</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.47916666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34700</v>
+        <v>60449</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54042</v>
+        <v>15000</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,30 +480,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -518,7 +538,12 @@
       <c r="B2" s="2" t="n">
         <v>45604.6875</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stadion An der Alten Försterei
@@ -549,24 +574,44 @@
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>591</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>20242025</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -581,7 +626,12 @@
       <c r="B3" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Vonovia Ruhrstadion
@@ -612,24 +662,28 @@
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>20242025</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -644,7 +698,12 @@
       <c r="B4" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -675,24 +734,28 @@
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>59</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>591</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>20242025</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -707,7 +770,12 @@
       <c r="B5" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
@@ -738,24 +806,28 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>59</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>591</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="R5" t="n">
         <v>20242025</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -770,7 +842,12 @@
       <c r="B6" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Weserstadion
@@ -801,24 +878,28 @@
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>59</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>591</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>20242025</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -833,7 +914,12 @@
       <c r="B7" s="2" t="n">
         <v>45605.60416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -864,24 +950,28 @@
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>59</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>591</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>20242025</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -927,24 +1017,28 @@
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>59</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>591</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>20242025</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -959,7 +1053,12 @@
       <c r="B9" s="2" t="n">
         <v>45606.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>MHPArena
@@ -990,24 +1089,28 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>59</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>591</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
         <v>20242025</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -1022,7 +1125,12 @@
       <c r="B10" s="2" t="n">
         <v>45606.64583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Voith-Arena
@@ -1053,24 +1161,497 @@
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>59</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>591</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>20242025</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>59</v>
+      </c>
+      <c r="P11" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>59</v>
+      </c>
+      <c r="P13" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>59</v>
+      </c>
+      <c r="P16" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>59</v>
+      </c>
+      <c r="P17" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
